--- a/excel-files/NAVOTAS/TANGOS ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/TANGOS ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0AFC29-ACA7-4699-8712-6BE513F3450F}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD78A733-2AB2-4737-BB9A-10F0A6435814}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Reading and Literacy</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t>Language</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -86,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -739,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -750,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3511,13 +3514,21 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="1">
+        <v>288</v>
+      </c>
+      <c r="D2" s="1">
+        <v>154</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
@@ -3529,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3549,15 +3560,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C4" s="1">
+        <v>288</v>
+      </c>
+      <c r="D4" s="1">
+        <v>36</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
@@ -3569,19 +3588,27 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C5" s="1">
+        <v>288</v>
+      </c>
+      <c r="D5" s="1">
+        <v>480</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.149999999999999">
@@ -3589,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3634,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -3654,7 +3681,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3674,19 +3701,27 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C11" s="1">
+        <v>350</v>
+      </c>
+      <c r="D11" s="1">
+        <v>438</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3694,7 +3729,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -3739,7 +3774,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3759,7 +3794,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3779,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3799,7 +3834,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3819,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3849,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3869,7 +3904,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>385</v>
@@ -3881,7 +3916,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3892,24 +3927,32 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>385</v>
+      </c>
+      <c r="D23" s="1">
+        <v>522</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1">
@@ -3917,7 +3960,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>385</v>
@@ -3926,10 +3969,10 @@
         <v>512</v>
       </c>
       <c r="E24" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3945,7 +3988,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1">
         <v>385</v>
@@ -3957,7 +4000,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -3973,7 +4016,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>385</v>
@@ -3985,7 +4028,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4001,7 +4044,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1">
         <v>385</v>
@@ -4013,7 +4056,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4029,7 +4072,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4049,19 +4092,27 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="C29" s="1">
+        <v>385</v>
+      </c>
+      <c r="D29" s="1">
+        <v>522</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4079,19 +4130,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>316</v>
+      </c>
+      <c r="D31" s="1">
+        <v>392</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4099,7 +4158,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4119,7 +4178,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -4139,7 +4198,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -4159,19 +4218,27 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C35" s="1">
+        <v>316</v>
+      </c>
+      <c r="D35" s="1">
+        <v>391</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4179,19 +4246,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>316</v>
+      </c>
+      <c r="D36" s="1">
+        <v>392</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4199,19 +4274,27 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="C37" s="1">
+        <v>316</v>
+      </c>
+      <c r="D37" s="1">
+        <v>392</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4219,19 +4302,27 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="C38" s="1">
+        <v>316</v>
+      </c>
+      <c r="D38" s="1">
+        <v>392</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4239,7 +4330,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -4269,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4289,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4309,7 +4400,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -4329,7 +4420,7 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4349,7 +4440,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -4369,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4389,7 +4480,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4409,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -4429,7 +4520,7 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -4459,7 +4550,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4479,7 +4570,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4499,7 +4590,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
@@ -4519,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -4539,7 +4630,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -4559,7 +4650,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4579,7 +4670,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -4599,7 +4690,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
@@ -4619,7 +4710,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -4649,7 +4740,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4669,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4689,7 +4780,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -4709,7 +4800,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
@@ -4729,7 +4820,7 @@
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4749,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4769,7 +4860,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
@@ -4789,7 +4880,7 @@
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4809,7 +4900,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -4839,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4859,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4879,7 +4970,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
@@ -4899,7 +4990,7 @@
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
@@ -4919,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -4939,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -4959,7 +5050,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
@@ -4979,7 +5070,7 @@
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -4999,7 +5090,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
@@ -5029,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5049,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5069,7 +5160,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
@@ -5089,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
@@ -5109,7 +5200,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5129,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5149,7 +5240,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
@@ -5169,7 +5260,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5189,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
@@ -5216,10 +5307,10 @@
     </row>
     <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5236,10 +5327,10 @@
     </row>
     <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5256,10 +5347,10 @@
     </row>
     <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5276,10 +5367,10 @@
     </row>
     <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -5296,10 +5387,10 @@
     </row>
     <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -5316,10 +5407,10 @@
     </row>
     <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -5336,10 +5427,10 @@
     </row>
     <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5356,10 +5447,10 @@
     </row>
     <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5381,10 +5472,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E91:E98 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E2:E6 E21:E29 E14:E19 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5397,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5427,38 +5518,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5471,81 +5562,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
+      <c r="N2" s="40" t="s">
+        <v>48</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y2" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>59</v>
       </c>
+      <c r="Z2" s="41" t="s">
+        <v>60</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -5696,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -5765,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -5834,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -5903,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -5972,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6041,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6110,7 +6201,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6187,7 +6278,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6261,7 +6352,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -6330,7 +6421,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -6394,24 +6485,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C17" s="1">
+        <v>350</v>
+      </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6419,11 +6512,18 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+        <v>2800</v>
+      </c>
+      <c r="K17" s="5">
+        <f>350*8</f>
+        <v>2800</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -6434,14 +6534,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6449,14 +6549,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
@@ -6468,7 +6568,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -6532,24 +6632,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C19" s="1">
+        <v>350</v>
+      </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6557,11 +6659,18 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="5"/>
+        <v>2800</v>
+      </c>
+      <c r="K19" s="5">
+        <f>350*8</f>
+        <v>2800</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
@@ -6572,14 +6681,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6587,14 +6696,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
@@ -6606,7 +6715,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6675,7 +6784,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -6827,7 +6936,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -6896,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -6965,7 +7074,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7034,7 +7143,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -7103,7 +7212,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -7172,7 +7281,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7241,7 +7350,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7310,7 +7419,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -7393,7 +7502,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7462,7 +7571,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7531,7 +7640,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -7600,7 +7709,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -7669,7 +7778,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -7738,7 +7847,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -7807,7 +7916,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -7876,7 +7985,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="5">
@@ -7945,7 +8054,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -8023,24 +8132,26 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C43" s="1">
+        <v>316</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8048,29 +8159,36 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+        <v>2528</v>
+      </c>
+      <c r="K43" s="5">
+        <f>326*8</f>
+        <v>2608</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8078,14 +8196,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
@@ -8097,7 +8215,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8161,24 +8279,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C45" s="1">
+        <v>316</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8186,29 +8306,36 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="5"/>
+        <v>2528</v>
+      </c>
+      <c r="K45" s="5">
+        <f>326*8</f>
+        <v>2608</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8216,14 +8343,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2528</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
@@ -8235,7 +8362,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -8304,7 +8431,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -8373,7 +8500,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8442,7 +8569,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -8511,7 +8638,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -8580,7 +8707,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -8663,7 +8790,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8732,7 +8859,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -8801,7 +8928,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -8870,7 +8997,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -8939,7 +9066,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -9008,7 +9135,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9077,7 +9204,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -9146,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -9215,7 +9342,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="5">
@@ -9298,7 +9425,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9367,7 +9494,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9436,7 +9563,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -9505,7 +9632,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -9574,7 +9701,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -9643,7 +9770,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -9712,7 +9839,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -9781,7 +9908,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -9850,7 +9977,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -9933,7 +10060,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10002,7 +10129,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10071,7 +10198,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10140,7 +10267,7 @@
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10209,7 +10336,7 @@
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10278,7 +10405,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10347,7 +10474,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10416,7 +10543,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10485,7 +10612,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -10568,7 +10695,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10637,7 +10764,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10706,7 +10833,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -10775,7 +10902,7 @@
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -10844,7 +10971,7 @@
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -10913,7 +11040,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -10982,7 +11109,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11051,7 +11178,7 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11120,7 +11247,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11203,7 +11330,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11272,7 +11399,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11341,7 +11468,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11410,7 +11537,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11479,7 +11606,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11548,7 +11675,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -11617,7 +11744,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -11686,7 +11813,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -11755,7 +11882,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -11835,10 +11962,10 @@
     </row>
     <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -11904,10 +12031,10 @@
     </row>
     <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -11973,10 +12100,10 @@
     </row>
     <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12042,10 +12169,10 @@
     </row>
     <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12111,10 +12238,10 @@
     </row>
     <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12180,10 +12307,10 @@
     </row>
     <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12249,10 +12376,10 @@
     </row>
     <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12318,10 +12445,10 @@
     </row>
     <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -13385,191 +13512,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="C2:C3 C14:C16 C23:C31 C33:C41 C44 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C46:C51 C18 C20:C21" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 K43:L51 K14:L21" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C45 C43" name="Textbooks_1"/>
+    <protectedRange sqref="C17" name="Textbooks_2"/>
+    <protectedRange sqref="C19" name="Textbooks_3"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13582,8 +13532,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13601,7 +13551,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13631,38 +13581,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13675,76 +13625,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
+      <c r="N2" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y2" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
+      <c r="Z2" s="41" t="s">
+        <v>86</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -13821,7 +13771,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5">
@@ -13890,7 +13840,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5">
@@ -13959,7 +13909,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -14028,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -14097,7 +14047,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14166,7 +14116,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14235,7 +14185,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14374,7 +14324,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -14443,7 +14393,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -14512,7 +14462,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -14581,7 +14531,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -14650,7 +14600,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14719,7 +14669,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -14788,7 +14738,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -14927,7 +14877,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -14996,7 +14946,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -15065,7 +15015,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15134,7 +15084,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -15203,7 +15153,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15272,7 +15222,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15341,7 +15291,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15410,7 +15360,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15480,7 +15430,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15549,7 +15499,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15618,7 +15568,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -15687,7 +15637,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -15756,7 +15706,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -15825,7 +15775,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -15894,7 +15844,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15963,7 +15913,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16032,7 +15982,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -16101,7 +16051,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16170,7 +16120,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16240,7 +16190,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16309,7 +16259,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16378,7 +16328,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -16447,7 +16397,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -16516,7 +16466,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -16585,7 +16535,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -16654,7 +16604,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16723,7 +16673,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16792,7 +16742,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -16861,7 +16811,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16930,7 +16880,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17000,7 +16950,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -17069,7 +17019,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17138,7 +17088,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -17207,7 +17157,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -17276,7 +17226,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -17345,7 +17295,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17414,7 +17364,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17483,7 +17433,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17552,7 +17502,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="5">
@@ -17621,7 +17571,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17690,7 +17640,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17760,7 +17710,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17829,7 +17779,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -17898,7 +17848,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -17967,7 +17917,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18036,7 +17986,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -18105,7 +18055,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18174,7 +18124,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18243,7 +18193,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18312,7 +18262,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18381,7 +18331,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18450,7 +18400,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18520,7 +18470,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18589,7 +18539,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18658,7 +18608,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -18727,7 +18677,7 @@
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -18796,7 +18746,7 @@
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -18865,7 +18815,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -18934,7 +18884,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19003,7 +18953,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19072,7 +19022,7 @@
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19141,7 +19091,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19210,7 +19160,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19280,7 +19230,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19349,7 +19299,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19418,7 +19368,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -19487,7 +19437,7 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19556,7 +19506,7 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19625,7 +19575,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19694,7 +19644,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19763,7 +19713,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19832,7 +19782,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -19901,7 +19851,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19970,7 +19920,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20040,7 +19990,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20109,7 +20059,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20178,7 +20128,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -20247,7 +20197,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20316,7 +20266,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20385,7 +20335,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -20454,7 +20404,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20523,7 +20473,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20592,7 +20542,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -20661,7 +20611,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20730,7 +20680,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20797,10 +20747,10 @@
     <row r="114" spans="1:28" s="7" customFormat="1"/>
     <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -20866,10 +20816,10 @@
     </row>
     <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -20935,10 +20885,10 @@
     </row>
     <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21004,10 +20954,10 @@
     </row>
     <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21073,10 +21023,10 @@
     </row>
     <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21142,10 +21092,10 @@
     </row>
     <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21211,10 +21161,10 @@
     </row>
     <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21280,10 +21230,10 @@
     </row>
     <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21858,186 +21808,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22055,8 +21825,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
